--- a/光伏配储项目/电价数据/2026/凤安站.xlsx
+++ b/光伏配储项目/电价数据/2026/凤安站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.48573</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38451</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7524999999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5444199999999999</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.55972</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.48654</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.47548</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.42624</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.44117</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.41831</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.41082</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.4093</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.39904</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.38988</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.37774</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.39224</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.41083</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.3836</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.37782</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.40804</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.38471</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.41146</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.40519</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.41474</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.40424</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.4314</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.47533</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.36429</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.23605</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.23199</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.13966</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.24819</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.00975</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.10872</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.07062</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.18947</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.19312</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.17887</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28948</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.16932</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.06839000000000001</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.39064</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.5159600000000001</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.5361900000000001</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.73339</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.12216</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39468</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.18812</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43134</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43764</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.66086</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.8644299999999999</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.47296</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.1957</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.40528</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.27337</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.9799</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.28062</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.46954</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.43604</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6820900000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.73214</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.07546</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.95259</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.8923</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.8000499999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.76079</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5141</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48311</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46408</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41748</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42735</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.71626</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8886499999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.94102</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5021100000000001</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52399</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50884</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50897</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40222</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47254</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38303</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.42355</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.36423</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36428</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.40272</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.39069</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.37879</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.39294</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.44281</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.12653</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.05108</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.48839</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.48363</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.3794</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.41585</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50473</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33379</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.31414</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.20873</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.22215</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29785</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.2922</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.26096</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.5545399999999999</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.7445700000000001</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.03148</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>-0.00893</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.7161900000000001</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.61497</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.04194</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.47902</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.8348099999999999</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.29894</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.25758</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.39054</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.36399</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.45007</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.67147</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.5907899999999999</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.74024</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.7493</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.15909</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.23595</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.12809</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.8349299999999999</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20321</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.10448</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.25565</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.02198</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.08868</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.65004</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.98153</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.91318</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.9551499999999999</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.7744500000000001</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.8951</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.74237</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.77714</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45084</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.73429</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.7674</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45087</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42963</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44498</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35557</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.3349</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5126000000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.4928</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48895</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36597</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44394</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41513</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36923</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39143</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38481</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36466</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43119</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.4472</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33642</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37197</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39846</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36879</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35725</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36291</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.37695</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.36454</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.3896</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39928</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47726</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44615</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44125</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35376</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36709</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.23001</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.24113</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.21184</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.0232</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.20784</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.25309</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.04834</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.02236</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.53814</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.21455</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.5015500000000001</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.57237</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.45952</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7777999999999999</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.4642</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.5374</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.41029</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.45537</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>-0.03506</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42839</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.42852</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.45957</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.45869</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.5405800000000001</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.53703</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.45424</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.47539</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.28202</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.62049</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.6451699999999999</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46595</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50588</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.47574</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.49591</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.6196799999999999</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.30166</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.39536</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42317</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.48232</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6167699999999999</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.57936</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.5579700000000001</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.72127</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.6061599999999999</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5232</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.42437</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.55996</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43324</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45831</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36177</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3423</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5136499999999999</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.50284</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.43813</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39354</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39248</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39969</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36164</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39282</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39039</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36634</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45193</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36395</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36797</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36104</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33444</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38938</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39046</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35255</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37895</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39659</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42028</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.43103</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.40287</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.34354</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.16581</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.11909</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.2515</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.27931</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.11551</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.5562699999999999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.2356</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.38148</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.29204</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.16906</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.15125</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.09320000000000001</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.30291</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.39552</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6232000000000001</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.29813</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.44802</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.38006</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.40671</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.28119</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.30258</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.30848</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.40548</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.47426</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.44816</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.50849</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45122</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46655</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40203</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47497</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.4904</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.55122</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.43794</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.55636</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.49311</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.4675</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50496</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.4253</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.40489</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.40046</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.42206</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34471</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.3195</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32053</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37228</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38155</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33817</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31734</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31541</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.3088399999999999</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31318</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31431</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.29014</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.30331</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.28296</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.30237</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.29705</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.18195</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.2674</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.08757</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.26634</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.16313</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.10665</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13091</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.17228</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04652000000000001</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.0112</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.20078</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.19993</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.08204</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.02836</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.0384</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.01604</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.23969</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29655</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29913</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.2955</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30242</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.4163</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.41748</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.41505</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.39224</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.36672</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.42812</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.42107</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.43404</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.48404</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38515</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.41245</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.42089</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.54071</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.36167</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35813</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.369</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.83211</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.45344</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.55584</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.51737</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.37812</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.39689</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.37339</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.40817</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.4178</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.4127</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.57755</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3632</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.36398</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.35103</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.39375</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.37374</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.39163</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.40156</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.38671</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.39249</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.41793</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.34215</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.1022</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04322</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04491</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.28469</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00452</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.19572</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04404</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.25995</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.1503</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04334</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.0285</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.04987</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.04804</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19974</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.35459</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.37685</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.34592</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.3227</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.42813</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.36215</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27067</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29724</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.37365</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38032</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42892</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45762</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.3919</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40239</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15655</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29424</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38544</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7854500000000001</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92038</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.91418</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86286</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29619</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88746</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18704</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86919</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.57586</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33081</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03288</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307500000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79095</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5421</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729400000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77752</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87385</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49312</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39864</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39985</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.4499</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20695</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62181</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43713</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45036</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41996</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.36452</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40376</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.37148</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38874</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.42924</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.45265</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.3985</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3455299999999999</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.44956</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.37143</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.41954</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.44182</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.65762</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.49454</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.62393</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.80524</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.88375</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47083</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.48681</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.65607</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.4928</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.02589</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.78059</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.87191</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8750399999999999</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.35434</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.50598</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.87749</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.8131799999999999</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.5888600000000001</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32082</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31967</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.36524</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29598</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.38773</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.34657</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.3479100000000001</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.37033</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.36665</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.34645</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.35802</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.46769</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.4716</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.52918</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.47507</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.43771</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.42045</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.36947</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9339500000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.38869</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.5206799999999999</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.46714</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.45098</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.54115</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.41808</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4618</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.38467</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.39348</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37237</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.3744</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.38728</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.45839</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.5991799999999999</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.38551</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.43633</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.36824</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.37936</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.38633</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.40995</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.38922</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.39491</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.33749</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.35838</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.35548</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.37239</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29453</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31158</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.2313</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28571</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30405</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30915</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.30758</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.2736</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29161</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26868</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20055</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29901</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28531</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.36968</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.4334</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.33834</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.30514</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.34595</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29207</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37414</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25822</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.37881</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35828</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27927</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.38414</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.37898</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.42572</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.37342</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.5224500000000001</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.36701</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.36798</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42721</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.47109</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.36522</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.46959</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.3767</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.45498</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.45631</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.7594</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.42202</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.94029</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.47604</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.19729</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.72623</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.81802</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6775099999999999</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.77485</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.5782</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.47299</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5239400000000001</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.46177</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.49009</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.43697</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.43285</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.47156</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5998600000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.43253</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.45469</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.47533</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.45426</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.40737</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.50301</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.5370199999999999</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.41557</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.44225</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.51073</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.43248</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.42932</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.45978</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.50026</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.41802</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.46543</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.51455</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.37911</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.44477</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.31594</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.42144</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.40146</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.36221</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31524</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.61995</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.38085</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.52707</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25144</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15559</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.28858</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.2755</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.02049</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.3014</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26406</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25853</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28431</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29926</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29787</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.33646</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.36746</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.36583</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.44405</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.44159</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.37877</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.3713399999999999</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.38825</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.40736</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.39115</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.64218</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.53762</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.9997</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.54355</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.5108199999999999</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.4129</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.50338</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.42507</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.40095</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.35582</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.38024</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.36401</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.50641</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.38587</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.39636</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.4367</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.40117</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.40381</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.40493</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.39841</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.41654</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.36833</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.41359</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.41333</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.51332</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.39682</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.4997200000000001</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.5232</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.43147</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.5127200000000001</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.48033</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.39579</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.41922</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.3652</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.43123</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.39483</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.35777</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.39756</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.33379</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.21594</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.08248</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.10694</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28314</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.12289</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.09293000000000001</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.09953000000000001</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.26469</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.11002</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.23283</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.09618</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25629</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.29336</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.13558</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.06346</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.04224</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.07423</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.0674</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.16763</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.08575000000000001</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28782</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.37003</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.39277</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.38761</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.38592</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.42015</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.4203</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.44813</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.39662</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.43273</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.5323300000000001</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.45575</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.4397799999999999</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.4586</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.44957</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.5321699999999999</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.51847</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.51489</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.52125</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.4599</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.41981</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.40767</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.41419</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.40794</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.39913</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.40052</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.3851</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.36577</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.66143</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.40472</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.5542999999999999</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.48583</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.47468</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.40897</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.42444</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.4215</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.43969</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.3956</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.38617</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.41925</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.39005</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.43674</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.40631</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.42518</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.3752799999999999</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.38543</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.37204</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.37722</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.53123</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.41092</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.42374</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.39292</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.36728</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.36429</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.3712</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37795</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.30621</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31458</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.30112</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.26725</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.26756</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.23925</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.17452</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.22461</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.1955</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30147</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31532</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.2402</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.29165</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29109</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27188</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.25501</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.35326</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.55015</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.3662</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.40206</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.36756</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.36245</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.37617</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.40247</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.5056499999999999</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.41481</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.38157</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.38943</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.40247</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.37714</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.38604</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.38327</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.46535</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.36165</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.39363</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.39695</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.38269</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.43052</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.41923</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.42578</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.37447</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.39009</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.39731</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.6160099999999999</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.38665</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.62405</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.41778</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.41478</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.39629</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.38689</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.36847</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.37688</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.37667</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.3628</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.36842</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.36242</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.3657</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.37933</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.42883</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.39603</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.41344</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.40809</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.36301</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.39743</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.38692</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.45203</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.12653</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.43153</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.67252</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.36657</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.51363</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.46579</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.40989</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.45604</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.41462</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.43069</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25901</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.25855</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.16285</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.1656</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.27068</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.24897</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.5353600000000001</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.2854100000000001</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.34525</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.2886</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.42654</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.12071</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.34235</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.38566</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.43046</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.57109</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.47685</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.46181</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.44329</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7155</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.38627</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.01442</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.86926</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.70452</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.39091</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.52585</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.26661</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.40518</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.36354</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.6227200000000001</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.41253</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.39456</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.50482</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.42409</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.38275</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.38486</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.41776</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.42259</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.39461</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.3757</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.4074700000000001</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.41973</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.33925</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.4072</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.41117</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.41852</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.43112</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.45051</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.43107</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.42489</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.38079</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.3687</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.37192</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39653</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.39688</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.4254</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.36331</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.36374</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.36543</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.35415</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.37338</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.37257</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.30006</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33271</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.34545</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.36665</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.35478</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.39319</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.37762</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.36753</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.3682</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.37553</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.37746</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.46019</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.36174</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.40624</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.42358</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.38552</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.37743</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.41691</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.41902</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.37844</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.45147</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.43829</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.38819</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.37173</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.43538</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.38565</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.44484</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.45185</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.36636</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.41187</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.36595</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.36519</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.36667</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.36671</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.36713</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.36633</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.38682</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.56449</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.36331</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.38203</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.38428</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.37152</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.35633</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.41612</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.36842</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.3853</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.3646</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.37586</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.36133</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.36403</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.38196</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.38223</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.37264</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.35781</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.38365</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.36638</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.3632</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34554</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33628</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37058</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31181</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.37953</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.37615</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.37053</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.37592</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.3837</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.36617</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.38408</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.36398</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.38248</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.37804</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.36501</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.42285</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.41599</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.41725</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.48296</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.4316</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.41151</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.39209</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6723600000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.03636</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.5139600000000001</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.5344800000000001</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.44206</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.36665</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.36291</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.37527</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.37009</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.42786</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.39777</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.37877</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.37591</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.37557</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.37874</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.37482</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.38551</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.3757</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.37671</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.38717</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.3728399999999999</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.38612</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3762</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.36424</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.41926</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.3755</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.37679</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.41832</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.3826</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.37329</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.3679</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.37463</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.36703</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.36197</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26201</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.11534</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30459</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.2329</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.20425</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.13698</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.21824</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.25069</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.25247</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.2562</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.16346</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.22282</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.26236</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.25283</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29193</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.27792</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.29995</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.40615</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.2821</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29251</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29642</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.36503</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.37862</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.38667</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.34321</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33314</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.3925</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.37374</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.42005</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.45799</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.5493400000000001</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.49377</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.4655899999999999</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.67762</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.63515</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.65278</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.62883</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.8459500000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.6042999999999999</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.14932</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.64562</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.5212</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.43289</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.41872</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.45017</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.5892500000000001</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.49407</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.47652</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.41121</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.39556</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.38577</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.57759</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.70731</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.61634</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.47012</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.47175</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.44851</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.46195</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.45596</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.46995</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.44177</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.41103</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.45279</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.45026</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.43103</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.40441</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.47905</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.43146</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.47621</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.43521</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.46248</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.45358</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.46917</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.45793</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.54416</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.53362</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.70796</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.6073500000000001</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.52813</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.59685</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.52444</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.45963</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.37562</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.40894</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.42277</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.45946</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.45875</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5401699999999999</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.45094</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.41372</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.3727</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.38672</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.46045</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.44108</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.42809</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.37293</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.29605</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.39558</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.6461</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.36445</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.70486</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.37812</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.40227</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.29645</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33827</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.36259</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.40421</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.37614</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.41042</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.41336</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.42429</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.43095</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.35402</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.46397</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.49866</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.58401</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.52527</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.62087</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.62285</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.68559</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.91687</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.13141</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.24818</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.90339</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.0629</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.88607</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.6720900000000001</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.10354</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.78589</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6394099999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.68865</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.54342</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.57404</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.57396</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.5630299999999999</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.55488</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.46986</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.67613</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.48694</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.50858</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.5319199999999999</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45074</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.44069</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.5175299999999999</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.43241</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.44671</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.5595800000000001</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.45876</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.46748</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.44415</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.42916</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.4133</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.41074</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.3765</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.38228</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.5858</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.42392</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.40229</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.37616</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.38228</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.44734</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.44945</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.39582</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.40763</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.37769</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.37146</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.39582</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40781</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.40279</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40235</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.4159</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.43559</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.40306</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.39472</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.39622</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.24579</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.40981</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.02782</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.22048</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36327</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.36169</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.5087</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.40809</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>7.000000000000001e-05</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.11751</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.03235</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29161</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.37369</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.38152</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.37395</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.40923</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.42596</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.4382799999999999</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.39686</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.48055</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.45634</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.45145</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43379</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.51297</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.42435</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.4596</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.47838</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.48857</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.50469</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.48573</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.39415</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.45263</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.39324</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.46479</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.42649</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.37806</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.4619</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.49238</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.46719</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.5097200000000001</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.49095</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.45246</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.40839</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.60788</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.45952</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.48059</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.48416</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.46778</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.45192</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.59023</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.40966</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.56104</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.55547</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.45157</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.56786</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.42706</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.45095</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.53186</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.42801</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.43895</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.42008</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.43303</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.4393</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.44557</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.5174500000000001</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.45185</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.51575</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.52971</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.47698</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.39315</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.40899</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.52879</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.36662</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29756</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.18779</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.21464</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.21612</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.26584</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.41618</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.23246</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.06698999999999999</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29696</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.27143</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.10048</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.11922</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.29688</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.18971</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.22796</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.27193</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.21703</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27658</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28571</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.35406</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.38578</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.37555</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.41708</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.38261</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.42498</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.37917</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.43808</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.45136</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.39536</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.44268</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.40394</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.44143</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.40834</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.46065</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.48386</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.45767</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.41354</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.43338</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.43154</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.39003</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.42472</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.47218</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.48684</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.39762</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.4472</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.38637</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.44781</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.41486</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.37404</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.37454</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.37402</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.37646</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.37352</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.49032</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.39745</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.39159</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.48033</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.36161</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.36179</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.45713</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.49011</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.48256</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.48256</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.47664</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.47664</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.48019</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.48291</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.47664</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.47722</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.38199</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.49039</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.48998</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.49447</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.29211</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.38623</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.03142</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00041</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00104</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15129</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02294</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03959</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01495</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04311</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04106</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04864</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.0483</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02445</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.0295</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.03643</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00142</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.2794</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03617</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01522</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03558</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20565</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26909</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29235</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28034</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.48752</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.36485</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.36954</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.37727</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.39399</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.3863</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.39371</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.36669</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38318</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.41612</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.52737</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.38875</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.42273</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.38567</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.38441</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.3824</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.38568</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.4025</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.13935</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.9815199999999999</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.48313</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.82594</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.5122899999999999</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.5275</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.57847</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.44147</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.4905</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.36729</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.45339</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.46607</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.46072</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.5982499999999999</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.44763</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.42247</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.6196499999999999</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.5328999999999999</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.60915</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.5585800000000001</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.6123500000000001</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.57989</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.56768</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.5913099999999999</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.6306499999999999</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.46304</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.51861</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.40682</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.37211</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.55692</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.50591</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.41325</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.34474</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.9088999999999999</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8748400000000001</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.41356</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.23023</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.88354</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.4459</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.07931999999999999</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.04604</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.00259</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>-0.007549999999999999</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.12075</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.04804</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.04845</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.04268</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-0.04489</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.04865</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.04783</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30689</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.00613</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25439</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29182</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.39341</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.36407</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.42176</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.44133</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.40663</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.39325</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.44287</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.01484</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.1071</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.07195</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.99758</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.0219</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.10572</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.86021</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.8584700000000001</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8625900000000001</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.9594600000000001</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.09637</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.10171</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.09173</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.39855</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.38924</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.41543</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.41527</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.5884299999999999</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.85973</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1.37358</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.8074</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.5161</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.60456</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.50564</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.50469</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40319</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.4733</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.51032</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.4019</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.40007</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.41611</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.63895</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.43204</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.45375</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.42238</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.44131</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.44631</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.5804</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.51359</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.48755</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.48885</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.59741</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.64863</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.48096</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.5071100000000001</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.34334</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.39055</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.38366</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.71094</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.40049</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.8987200000000001</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.42236</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.52912</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.71409</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.18561</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.19376</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.13494</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.71157</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.39921</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.26966</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.29892</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26091</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31317</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30442</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30442</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.37485</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.37524</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.4155</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.42505</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.4148</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.40963</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.41109</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.44842</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.61078</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>1.18641</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.49562</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.87812</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.59585</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.44048</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.5335700000000001</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.52461</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.47823</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.6538099999999999</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.40258</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.41894</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.39472</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.40501</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.39628</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.48961</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.50488</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.4765</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.46962</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.44747</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.44171</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.43613</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.41144</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.40225</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.39407</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.38598</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.36631</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.4021</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.37934</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.37812</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.37363</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.37424</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.37477</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.37485</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.38999</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.37837</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.4011</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.39121</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.40183</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.38608</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.39987</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.53291</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.42949</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.41188</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.82504</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.98717</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.80552</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.29236</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.75105</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.58108</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.40306</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.3842</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.36415</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36371</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.37938</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.37223</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.37701</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.41207</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.36816</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.29676</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.30482</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36446</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41919</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39043</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.41051</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.9148999999999999</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.8275</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.4408</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.45694</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.55874</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.5524600000000001</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.61576</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.8147799999999999</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.5534199999999999</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.8985700000000001</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.78062</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.59494</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.5969800000000001</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.43341</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.45167</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.5193</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.40722</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.38896</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.5268699999999999</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.44157</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.39446</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.4413</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.40892</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.27736</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.40254</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.38987</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.39776</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.52224</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.43658</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.44393</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.43151</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.42101</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.38565</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.41023</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.39032</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.41147</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.40978</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.40189</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.39391</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.38585</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.38463</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.38583</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.38556</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.37854</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.37656</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.37754</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.36557</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.39846</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.40743</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.45119</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.41514</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.38142</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.38175</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.37558</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.37417</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.40486</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39053</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.38995</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35328</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43401</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.38668</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.39081</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.37952</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.28228</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.39657</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.38059</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.3752200000000001</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29266</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31427</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.40615</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.39284</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.39556</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.40476</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.42955</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.39757</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.40929</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.44234</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.37898</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.52418</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.64175</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.41218</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.70616</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.75544</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.53711</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.44237</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.75961</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.48219</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.62763</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.9199700000000001</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.59741</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.57112</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.57214</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.98976</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.46686</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.48618</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.43186</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.3996499999999999</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.40268</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.39407</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.40169</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.39211</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38547</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.39752</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.37545</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.38229</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.39573</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.38759</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.37619</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.36861</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.36564</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.44891</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.39092</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.38423</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.5731900000000001</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.37952</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36454</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.38676</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.37326</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.41674</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.41156</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.40094</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.40263</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.38976</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.38652</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.4373</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.38643</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.38807</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.36555</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.16788</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.26631</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.28801</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.1695</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.18926</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.08581999999999999</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.18733</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.01658</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.04025</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.2931</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26322</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.00112</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.02781</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.02126</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.09904</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.02063</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>-0.008369999999999999</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.29164</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.2268</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.17592</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.20223</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.35466</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.3781600000000001</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.38888</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.42431</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.39254</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.38365</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.39121</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.39037</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.38753</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.36762</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.39705</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.41519</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.52763</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.43463</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.44674</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.51198</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.46874</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.4252</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.42004</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42201</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.40781</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.41673</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.44184</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38669</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.47249</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.40439</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.39664</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.38896</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.41359</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.22431</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.42683</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.27471</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.46959</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.42729</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.4023</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.4125</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.42125</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.41183</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.40689</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.40302</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.40124</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.39794</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.41251</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.40355</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.40147</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.39733</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.39468</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.39678</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.3959</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.39331</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.38702</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.39318</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.38616</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.40752</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.38569</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.38195</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.38705</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.3921</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.39301</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.3826</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.39341</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.32893</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.22688</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.29846</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.26543</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.28263</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.28688</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.28216</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.28508</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.13011</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.28496</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.15113</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.2692</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.30872</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35323</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.30287</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.41282</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.40821</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42264</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.42327</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.4285</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.37347</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.4039700000000001</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.40575</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.37897</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.37116</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.42811</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.43163</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.40351</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.41253</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39473</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.41762</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.40494</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.41565</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.37731</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.40919</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.4038</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.41272</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38504</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.38387</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.38405</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.38618</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.47805</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.40976</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.44612</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.40127</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.40093</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.40233</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.40665</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.40214</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.40323</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39401</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.39067</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.38548</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.40305</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.36197</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38923</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.39665</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.39488</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.38896</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.3875</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.38355</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.38521</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.38266</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17699</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30202</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29057</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14662</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19992</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.02322</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.24134</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.03408</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.02688</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.00646</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.02079</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.02556</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.13155</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.01833</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.06253</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.17465</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.01351</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22861</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26831</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15698</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.25957</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.31083</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.02207</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.21922</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.04063</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20084</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14762</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26393</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.25702</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.30337</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.41173</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.36657</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.37765</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.38013</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39294</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.36723</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.38925</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.4165</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.4151</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.41233</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.4219</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37567</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.40421</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.42605</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.41602</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40288</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.42774</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.50529</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39712</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41336</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.41572</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41333</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38133</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40151</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40743</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.4063</v>
       </c>
     </row>
   </sheetData>
